--- a/daily_matches/job_matches_2026-08-18.xlsx
+++ b/daily_matches/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>AmeriSave Mortgage</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Data Lake, Apache Airflow, CI/CD, Git, Snowflake, Databricks, Kafka</t>
+          <t>Data Scientist, LangChain, RAG, Mistral, Hugging Face, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dca464379b2183e</t>
+          <t>https://www.indeed.com/viewjob?jk=4ebe5e7eca797abc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer, Global Banking &amp; Markets, AI/ML Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>BioAgilytix Labs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL</t>
+          <t>Generative AI, S3, Glue, CI/CD, GitHub Actions, Git, Snowflake, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c0a2cfbacdbc262</t>
+          <t>https://www.indeed.com/viewjob?jk=7f99a8f1166781f9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Engineer - MLOps Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, NoSQL, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f288d344fe9b403b</t>
+          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data &amp; AI Analyst, Finance Systems</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TrueScripts Management Services</t>
+          <t>AeroVironment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, IN, US USA</t>
+          <t>Simi Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, CI/CD, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Prompt Engineering, CI/CD, Git, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+          <t>https://www.indeed.com/viewjob?jk=01ab4083a3713e89</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI and Automation Engineer</t>
+          <t>Sr. Frontend Engineer-Roundel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ericsson</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, AKS, Python, SQL, R, Scala</t>
+          <t>RAG, AKS, CI/CD, PostgreSQL, MongoDB, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bad5642e86b3dc24</t>
+          <t>https://www.indeed.com/viewjob?jk=a71a68acf7f1a39e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Engineer with Python/Shell Scripting</t>
+          <t>Software Engineer Sr- AI Agents / Generative AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, PySpark, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76b4b86f0ee35495</t>
+          <t>https://www.indeed.com/viewjob?jk=9d6d9c1e764b9fd3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Member Experience</t>
+          <t>Software Engineer- AI Agents / Generative AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>oura</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, AKS, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PySpark, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed07057291642c0</t>
+          <t>https://www.indeed.com/viewjob?jk=83dffd9294d88254</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer - Senior Associate - Commercial Technology &amp; Innovation</t>
+          <t>SRE Software Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, Snowflake, Databricks, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4cb3fb82506dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=7443708b6b1372cb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer- Experienced Associate- Commercial Technology &amp; Innovation</t>
+          <t>2027 Data &amp; AI Program - Summer Internship - Analyst - United States</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, Snowflake, Databricks, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,392 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445f7405d45308ad</t>
+          <t>https://www.indeed.com/viewjob?jk=da7b3dc73de1470e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chesapeake, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09a4e478c31c0565</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d19c2e903d090f00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7afab6c154eed635</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eac63d6809647e5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b222515a4e159f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49ad056b5209b2b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NewYork-Presbyterian Hospital</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Manhattan, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1343552027471cbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Java/Agentic)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>10</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Dataflow, BigQuery, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=193269c8462487d3</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5c0c522f4ece582</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Founding Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Broccoli AI</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b21d02873cf05123</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Application Security Engineer IV</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Application Security Engineer IV</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-18.xlsx
+++ b/daily_matches/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Data Engineer IV (6281)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AmeriSave Mortgage</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Mistral, Hugging Face, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+          <t>Generative AI, RAG, Prompt Engineering, BigQuery, CI/CD, Git, Snowflake, BigQuery, Kafka, Tableau</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ebe5e7eca797abc</t>
+          <t>https://www.indeed.com/viewjob?jk=2638fbb6172c3dae</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Web Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BioAgilytix Labs</t>
+          <t>Aeologic Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, S3, Glue, CI/CD, GitHub Actions, Git, Snowflake, Tableau, Power BI, Python</t>
+          <t>RAG, S3, Docker, CI/CD, Git, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f99a8f1166781f9</t>
+          <t>https://www.indeed.com/viewjob?jk=2414440e35559b28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Engineer - MLOps Platform</t>
+          <t>AI Systems &amp; Process Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>NorthStar Medical Radioisotopes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Beloit, WI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, Python</t>
+          <t>RAG, Copilot, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
+          <t>https://www.indeed.com/viewjob?jk=62ed3a53ca681978</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Analyst, Finance Systems</t>
+          <t>Logistics Engineer - Warehouse Process Specialist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AeroVironment</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Simi Valley, CA, US USA</t>
+          <t>Athens, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Prompt Engineering, CI/CD, Git, Tableau, Power BI, Python</t>
+          <t>RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ab4083a3713e89</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa35ac95d6760c1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Frontend Engineer-Roundel</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, AKS, CI/CD, PostgreSQL, MongoDB, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a71a68acf7f1a39e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbd91f33189501d6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer Sr- AI Agents / Generative AI</t>
+          <t>Senior Data Engineer - Data Quality and Governance</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, PySpark, Python, R, Scala, Optimization</t>
+          <t>RAG, Gemini, BigQuery, Apache Airflow, CI/CD, Git, BigQuery, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d6d9c1e764b9fd3</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer- AI Agents / Generative AI</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>MSA Safety</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Cranberry Township, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PySpark, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, Hugging Face, TensorFlow, PyTorch, CI/CD, Git, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83dffd9294d88254</t>
+          <t>https://www.indeed.com/viewjob?jk=b713a8a4f4c23ad6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SRE Software Engineer III</t>
+          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Synapse, Data Lake, Dataflow, Snowflake, Kafka, Power BI, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7443708b6b1372cb</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2027 Data &amp; AI Program - Summer Internship - Analyst - United States</t>
+          <t>Gen AI Software Development Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7b3dc73de1470e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7ed439cb3886b9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Savers/Value Village</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, TensorFlow, PyTorch, PySpark, Power BI, Python, SQL, R, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,357 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a4e478c31c0565</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Raleigh-Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d19c2e903d090f00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7afab6c154eed635</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eac63d6809647e5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b222515a4e159f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=49ad056b5209b2b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>NewYork-Presbyterian Hospital</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Manhattan, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1343552027471cbf</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Engineer II (Java/Agentic)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f5c0c522f4ece582</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Founding Data Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Broccoli AI</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b21d02873cf05123</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Application Security Engineer IV</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Application Security Engineer IV</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=097e389d56a39bb7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-18.xlsx
+++ b/daily_matches/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer IV (6281)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, BigQuery, CI/CD, Git, Snowflake, BigQuery, Kafka, Tableau</t>
+          <t>Data Scientist, RAG, CI/CD, Terraform, Git, Databricks, Kafka, Hadoop, Python, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2638fbb6172c3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfbd27edc96381f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aeologic Technologies Pvt Ltd</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,77 +521,77 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, Git, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2414440e35559b28</t>
+          <t>https://www.indeed.com/viewjob?jk=e622b2e76eb112c1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Systems &amp; Process Engineer</t>
+          <t>Agentic Product Builder, Sr. Associate - State Street Investment Managment</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NorthStar Medical Radioisotopes</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Beloit, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ed3a53ca681978</t>
+          <t>https://www.indeed.com/viewjob?jk=9b13632a778e2747</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Logistics Engineer - Warehouse Process Specialist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Athens, TX, US USA</t>
+          <t>Danbury, CT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Docker, Tableau, Matplotlib, Seaborn, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa35ac95d6760c1</t>
+          <t>https://www.indeed.com/viewjob?jk=7b22db6e78604b96</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbd91f33189501d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c85991fede412c04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Quality and Governance</t>
+          <t>Jr. AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Ambe Healthcare Staffing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Gemini, BigQuery, Apache Airflow, CI/CD, Git, BigQuery, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
+          <t>https://www.indeed.com/viewjob?jk=737d0ee379e07d5c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MSA Safety</t>
+          <t>CAMP Systems International, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cranberry Township, PA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Hugging Face, TensorFlow, PyTorch, CI/CD, Git, Python, SQL, R, Optimization</t>
+          <t>Copilot, S3, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b713a8a4f4c23ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=ccdd50d9f65ee45f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Dataflow, Snowflake, Kafka, Power BI, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Prompt Engineering, EC2, PostgreSQL, MongoDB, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
+          <t>https://www.indeed.com/viewjob?jk=89aecb3c13268aa0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gen AI Software Development Engineer</t>
+          <t>Senior Forward Deployed AI Engineer / Solutions Architect (GenAI, AWS)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7ed439cb3886b9</t>
+          <t>https://www.indeed.com/viewjob?jk=5e94aaaf58d73011</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Senior Forward Deployed AI Engineer / Solutions Architect (GenAI, AWS)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Savers/Value Village</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,262 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, PySpark, Power BI, Python, SQL, R, Optimization, Hypothesis Testing</t>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097e389d56a39bb7</t>
+          <t>https://www.indeed.com/viewjob?jk=477ad3d92dcf60c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Forward Deployed AI Engineer / Solutions Architect (GenAI, AWS)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Provectus</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4008236660a300da</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Forward Deployed AI Engineer / Solutions Architect (GenAI, AWS)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Provectus</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=184e6dceecb7e6e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Forward Deployed AI Engineer / Solutions Architect (GenAI, AWS)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Provectus</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3769ef635a3be053</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CAMP Systems International, Inc.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Merrimack, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>S3, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f54327e0d1921f6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Kubernetes, CI/CD, Git, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93be66d4ee62bf72</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Product Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94d46f516b6d0622</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, PySpark, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ad4a5d391e5cb08</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-18.xlsx
+++ b/daily_matches/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Terraform, Git, Databricks, Kafka, Hadoop, Python, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, S3, Glue, Data Lake, Docker, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfbd27edc96381f</t>
+          <t>https://www.indeed.com/viewjob?jk=93c578df954821f2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JACK Entertainment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL</t>
+          <t>RAG, Redshift, BigQuery, Synapse, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e622b2e76eb112c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ddeffbcda3a30081</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agentic Product Builder, Sr. Associate - State Street Investment Managment</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Git, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, S3, Data Lake, Docker, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b13632a778e2747</t>
+          <t>https://www.indeed.com/viewjob?jk=abd794d42375295b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Palantir Data engineer - Forward Deployment Engineers</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>AI SPINS INC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Danbury, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Tableau, Matplotlib, Seaborn, Python, SQL, R, Java</t>
+          <t>Glue, Redshift, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Redshift, PySpark, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b22db6e78604b96</t>
+          <t>https://www.indeed.com/viewjob?jk=a35bc9c9058b4a38</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>College Station, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, Docker, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c85991fede412c04</t>
+          <t>https://www.indeed.com/viewjob?jk=1b91c8cb08be11f5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jr. AI Engineer</t>
+          <t>Senior AI Engineer / AI Solutions Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ambe Healthcare Staffing</t>
+          <t>MLG Capital</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, CI/CD, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=737d0ee379e07d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=8030d426a9ed420d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CAMP Systems International, Inc.</t>
+          <t>HDR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Copilot, S3, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,357 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccdd50d9f65ee45f</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Agentic AI Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Catapult Sports</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, EC2, PostgreSQL, MongoDB, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=89aecb3c13268aa0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Forward Deployed AI Engineer / Solutions Architect (GenAI, AWS)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Provectus</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e94aaaf58d73011</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Forward Deployed AI Engineer / Solutions Architect (GenAI, AWS)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Provectus</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Newark, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=477ad3d92dcf60c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Forward Deployed AI Engineer / Solutions Architect (GenAI, AWS)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Provectus</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4008236660a300da</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Forward Deployed AI Engineer / Solutions Architect (GenAI, AWS)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Provectus</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=184e6dceecb7e6e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Forward Deployed AI Engineer / Solutions Architect (GenAI, AWS)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Provectus</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3769ef635a3be053</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CAMP Systems International, Inc.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Merrimack, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f54327e0d1921f6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Glendale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Kubernetes, CI/CD, Git, Kafka, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93be66d4ee62bf72</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Product Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94d46f516b6d0622</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Data Lake, PySpark, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad4a5d391e5cb08</t>
+          <t>https://www.indeed.com/viewjob?jk=3d7b851755f54eff</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-18.xlsx
+++ b/daily_matches/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer V, AI Digital &amp; Engineering Software</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>X-Energy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, S3, Glue, Data Lake, Docker, CI/CD, Jenkins, GitHub Actions</t>
+          <t>LangChain, RAG, LLaMA, S3, EC2, Glue, Athena, Data Lake, Kinesis, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c578df954821f2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a922959a62dc33f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer III, AI Digital &amp; Engineering Software</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JACK Entertainment</t>
+          <t>X-Energy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Synapse, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>LangChain, RAG, LLaMA, S3, EC2, Glue, Athena, Data Lake, Kinesis, FastAPI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddeffbcda3a30081</t>
+          <t>https://www.indeed.com/viewjob?jk=724dd35cc9ba9c68</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Optimal Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, S3, Data Lake, Docker, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd794d42375295b</t>
+          <t>https://www.indeed.com/viewjob?jk=5f701435c121d668</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Palantir Data engineer - Forward Deployment Engineers</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AI SPINS INC</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Glue, Redshift, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Redshift, PySpark, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, S3, EC2, Docker, CI/CD, Databricks, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35bc9c9058b4a38</t>
+          <t>https://www.indeed.com/viewjob?jk=68d8cb56e4fbc7eb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Data Scientist - Statistics/ML - Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>College Station, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Docker, Git, PostgreSQL, MySQL, Python, SQL</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Snowflake, Databricks, Hadoop, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b91c8cb08be11f5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc63a2b4350e9c2d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer / AI Solutions Architect</t>
+          <t>Junior Cloud Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MLG Capital</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Cortex, S3, Glue, Data Lake, Kinesis, CI/CD, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,602 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8030d426a9ed420d</t>
+          <t>https://www.indeed.com/viewjob?jk=f8a775008dff7530</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HDR</t>
+          <t>Bed Bath &amp; Beyond</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, TensorFlow, Keras, Docker, Kubernetes, Kafka, Hadoop, Cassandra, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e18063e9579ba86</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Automation Engineering</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NBCUniversal</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, Cortex, CI/CD, Snowflake, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57bf32982bd0fc09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>(USA) Senior, Software Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, Apache Airflow, CI/CD, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61a0a1e50277bf68</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>(USA) Senior, Software Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ddb74148473a593</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Java Full Stack Developer - Onsite : Dallas, TX</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4eb3cdf2006d3c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Whoop</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, EC2, CI/CD, Snowflake, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bcca80a49caf9b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hertz</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Estero, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Kinesis, Databricks, PySpark, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3cb1b92b52d7a99</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Software Engineer - Java developer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, Kafka, PostgreSQL, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f9d13ba7787f198</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Full stack Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16fcdf2dd99903d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tiger Analytics</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Redshift, Snowflake, Databricks, Redshift, Kafka, Hadoop, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06a5cdb578318149</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Applied Data Scientist</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CLAIR</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=035cafbd73583dde</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer - Java developer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, Kafka, PostgreSQL, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8418bc63c4e1211a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>VIE - Software Engineer (based in Miami)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pelico</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=072180860b5c5965</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Backend, AI Experiences &amp; AI Platform)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Whoop</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d7b851755f54eff</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kafka, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cb3c96e33e56ced</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sr. Evaluation Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LogicMonitor</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, MLflow, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4a23cf57be3f032</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sr. Data Architect, AI &amp; Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Avery Dennison</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5881054afe811fbd</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>U.S. Renal Care</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ee90956f51ee1bf</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-18.xlsx
+++ b/daily_matches/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer V, AI Digital &amp; Engineering Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>X-Energy</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, S3, EC2, Glue, Athena, Data Lake, Kinesis, FastAPI</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, XGBoost, BigQuery, Dataflow, MLflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a922959a62dc33f</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd78528f3cfeae1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III, AI Digital &amp; Engineering Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>X-Energy</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, S3, EC2, Glue, Athena, Data Lake, Kinesis, FastAPI</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, XGBoost, BigQuery, Dataflow, MLflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724dd35cc9ba9c68</t>
+          <t>https://www.indeed.com/viewjob?jk=a03747dc8123c18e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optimal Inc.</t>
+          <t>Arrive Logistics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Data Scientist, RAG, Gemini, Prompt Engineering, Cortex, Redshift, BigQuery, CI/CD, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f701435c121d668</t>
+          <t>https://www.indeed.com/viewjob?jk=4519eed0c0bcdda8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior AI Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, S3, EC2, Docker, CI/CD, Databricks, NoSQL</t>
+          <t>RAG, S3, EC2, Data Lake, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68d8cb56e4fbc7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=5c52720211e7a971</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist - Statistics/ML - Remote</t>
+          <t>Python/GenAI Solutions Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Snowflake, Databricks, Hadoop, NoSQL, Tableau</t>
+          <t>Generative AI, RAG, Copilot, S3, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc63a2b4350e9c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=6ddb4f1cd1354de8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Junior Cloud Data &amp; AI Engineer</t>
+          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Cortex, S3, Glue, Data Lake, Kinesis, CI/CD, Snowflake</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Snowflake, Databricks, Kafka, Hadoop, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8a775008dff7530</t>
+          <t>https://www.indeed.com/viewjob?jk=d45183e5b3bce9f1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Data Engineer (Adobe Experience Platform)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bed Bath &amp; Beyond</t>
+          <t>Merkle, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, Keras, Docker, Kubernetes, Kafka, Hadoop, Cassandra, Python, SQL</t>
+          <t>Data Scientist, Copilot, BigQuery, Apache Airflow, Snowflake, Databricks, BigQuery, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e18063e9579ba86</t>
+          <t>https://www.indeed.com/viewjob?jk=f1893b5f6e215827</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Automation Engineering</t>
+          <t>AI Foundational Model Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Cortex, CI/CD, Snowflake, Databricks, Python, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57bf32982bd0fc09</t>
+          <t>https://www.indeed.com/viewjob?jk=0257949e2e60f8da</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>(USA) Senior, Software Engineer</t>
+          <t>Senior Analytics Data Engineer - Homes.com</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, Apache Airflow, CI/CD, Git, Kafka, Python, R, Java</t>
+          <t>RAG, Gemini, Copilot, Prompt Engineering, Git, Snowflake, Databricks, PySpark, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a0a1e50277bf68</t>
+          <t>https://www.indeed.com/viewjob?jk=b80d45c896bb26ef</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>(USA) Senior, Software Engineer</t>
+          <t>Data Scientist - Hedging &amp; Risk Management (Renewables)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>ENGIE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, CI/CD, Git, Snowflake, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ddb74148473a593</t>
+          <t>https://www.indeed.com/viewjob?jk=274da568c14f4cc3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer - Onsite : Dallas, TX</t>
+          <t>GIS Software Engineer - Esri</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, R</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Terraform, Git, Snowflake, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eb3cdf2006d3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=21ac825d5b64f66f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>DevSecOps Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Whoop</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, CI/CD, Snowflake, Python, SQL, R, Java</t>
+          <t>Generative AI, LangChain, RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcca80a49caf9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=dae8b61c5a922e9a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer (Microsoft Azure)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estero, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Kinesis, Databricks, PySpark, Kafka, Python, R, Java</t>
+          <t>RAG, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cb1b92b52d7a99</t>
+          <t>https://www.indeed.com/viewjob?jk=7a0b93ee4cad8277</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer - Java developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, Kafka, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>AI Engineer, RAG, S3, Glue, Athena, Data Lake, CI/CD, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9d13ba7787f198</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed0d719f5bbccf0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, RAG, S3, Glue, Athena, Data Lake, CI/CD, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fcdf2dd99903d1</t>
+          <t>https://www.indeed.com/viewjob?jk=69ed747f2eb90e25</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer 2 - Supply Chain</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Redshift, Snowflake, Databricks, Redshift, Kafka, Hadoop, Python, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a5cdb578318149</t>
+          <t>https://www.indeed.com/viewjob?jk=d46a69a4b84ca4b4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Applied Data Scientist</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLAIR</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Snowflake, Python, SQL, R</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=035cafbd73583dde</t>
+          <t>https://www.indeed.com/viewjob?jk=b76b7b194c7c6249</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer - Java developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, Kafka, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8418bc63c4e1211a</t>
+          <t>https://www.indeed.com/viewjob?jk=a6573882e75f2256</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VIE - Software Engineer (based in Miami)</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pelico</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072180860b5c5965</t>
+          <t>https://www.indeed.com/viewjob?jk=afbb42f1fb391e5b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend, AI Experiences &amp; AI Platform)</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Whoop</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kafka, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cb3c96e33e56ced</t>
+          <t>https://www.indeed.com/viewjob?jk=b4774424a7c977d0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Evaluation Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, MLflow, CI/CD, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a23cf57be3f032</t>
+          <t>https://www.indeed.com/viewjob?jk=00673ec98ad396b2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Architect, AI &amp; Analytics Platforms</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Avery Dennison</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,42 +1231,2107 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5881054afe811fbd</t>
+          <t>https://www.indeed.com/viewjob?jk=0cca2406337e3f4b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Renal Care</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f87b401bf307b90</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e2545a3398f75f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da5709f322b6de77</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pierre, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33e7e2d41c6bbc1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bbf8d425b26cb57</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d8296a32cbcd5e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Hope Hull, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bddcc0bf9a07cf52</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87c76b5382d91ff5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Pawtucket, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2a46dfdabaf144b</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Hot Springs Village, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=148ea1e43d8803c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Jackson, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d122abea15bffcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Middletown, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9fb52081cc83a1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6585b0f7548a110e</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6af657ad808aca0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Charleston, WV, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c71c57379755325</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Augusta, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e4b1fb8cf73679e</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Kennesaw, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eef37f19b519cfb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2acd943bf9f49043</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Kansas City, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5356ec2fad3097c</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b0b088c77b432bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Fremont, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=502c66caf2321daa</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8e35eb0472f1b04</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Okemos, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ea808b55ddf87a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8d2fb8ee058fcb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31e2d771ef37e989</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Corrales, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5701765b8810e954</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a74fc9df8466ed80</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Upper Darby, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e350cbedde8fb5c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37c3d1a6e3db03ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fb7cf0d3892b335</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2515e91820622466</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Columbia, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f92266e4f2da0ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5834a6a46819e223</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>New Franken, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a21ae7255e004909</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d766b034a172a2ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Walnut Creek, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ab132d0ecb2e269</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=163d580eae60a657</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c8d43b4208b386a</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58a509ab2ac2911c</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=289f16a53bce28f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Associate Data Scientist</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Databricks, Hadoop, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce77d5f21bbbe186</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>DLA Piper</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, NLTK, Hadoop, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ff3acd515f85510</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Software Engineer III (Java &amp; AWS)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8182a3374008a264</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior RAPA Data Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Synapse, Data Lake, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e20027a6a5bcf1cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Software Developer II - Financials (Full Stack, Front End)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>National Information Solutions Cooperative (NISC)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Copilot, Kubernetes, Git, Databricks, Kafka, Cassandra, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6765e835ec8964bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; Analytics Specialist</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>HCVT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f592bdc647c7168e</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; Analytics Specialist</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>HCVT</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7667c063f1912012</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; Analytics Specialist</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>HCVT</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69003bb8af2a1f2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; Analytics Specialist</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>HCVT</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1f889d3f9116af0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; Analytics Specialist</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>HCVT</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Westlake Village, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9df31183a85e82ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NewYork-Presbyterian Hospital</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf557823600dd122</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Data Scientist-Senior Associate</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12d873b67b2c9ef4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Texas Health and Human Services Commission</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
         <v>10</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee90956f51ee1bf</t>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6011d6261bebf08d</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, FastAPI, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=003def57f4828a04</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>GovCloud Distributed Systems Software Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Copilot, Prompt Engineering, Docker, Kubernetes, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d699b5984c9fdd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, FastAPI, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f0042cd0ec794ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Authorized Officer, Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>UBS</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>CI/CD, Jenkins, Terraform, Git, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=287cb92545aca980</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ACI Worldwide</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8038fa4960949cc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>DevOps Engineer II</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CoStar Group</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ceedb22735e88882</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, MLflow, Kubernetes, Python, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b82fd3a5aaaf287</t>
         </is>
       </c>
     </row>
